--- a/data.mn/public/datasets/tourism-arrivals-monthly.xlsx
+++ b/data.mn/public/datasets/tourism-arrivals-monthly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,22 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,14 +416,18 @@
   </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tourists</t>
         </is>
@@ -612,14 +606,18 @@
   </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>жуулчид</t>
         </is>
